--- a/tests/fixtures/12_multi_sheet/12_multi_sheet_pattern-from-claude.xlsx
+++ b/tests/fixtures/12_multi_sheet/12_multi_sheet_pattern-from-claude.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Q1 2026 Summary</t>
+          <t>Department:</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Department:</t>
+          <t>Cost Centre:</t>
         </is>
       </c>
     </row>
